--- a/ED_Fig2lm.xlsx
+++ b/ED_Fig2lm.xlsx
@@ -497,34 +497,34 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>47.49347560183979</v>
+        <v>48.74870365513287</v>
       </c>
       <c r="C3">
-        <v>6.032629333182033</v>
+        <v>6.040440637918716</v>
       </c>
       <c r="D3">
-        <v>67.00602469565526</v>
+        <v>62.17832322895111</v>
       </c>
       <c r="E3">
-        <v>6.110076467854176</v>
+        <v>6.109727847288294</v>
       </c>
       <c r="F3">
-        <v>61.99850621208581</v>
+        <v>59.02880206625683</v>
       </c>
       <c r="G3">
-        <v>6.109674985810381</v>
+        <v>6.111088779521249</v>
       </c>
       <c r="H3">
-        <v>58.83266883652696</v>
+        <v>56.65194298344693</v>
       </c>
       <c r="I3">
-        <v>8.274530711808929</v>
+        <v>5.734443582366842</v>
       </c>
       <c r="J3">
-        <v>6.084126928948863</v>
+        <v>6.08708575490942</v>
       </c>
       <c r="K3">
-        <v>0.03641466805451493</v>
+        <v>0.03298775771346076</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -567,34 +567,34 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>81.73198824643205</v>
+        <v>82.42895715553374</v>
       </c>
       <c r="C5">
-        <v>5.720072786211963</v>
+        <v>5.729755605364584</v>
       </c>
       <c r="D5">
-        <v>98.81967973842349</v>
+        <v>95.60611028889988</v>
       </c>
       <c r="E5">
-        <v>5.722875216979426</v>
+        <v>5.721788312286554</v>
       </c>
       <c r="F5">
-        <v>85.9923802470679</v>
+        <v>84.67757878051907</v>
       </c>
       <c r="G5">
-        <v>5.738533239370229</v>
+        <v>5.74211332640529</v>
       </c>
       <c r="H5">
-        <v>88.84801607730782</v>
+        <v>87.57088207498423</v>
       </c>
       <c r="I5">
-        <v>7.262382167837291</v>
+        <v>5.755446356299833</v>
       </c>
       <c r="J5">
-        <v>5.727160414187206</v>
+        <v>5.731219081352143</v>
       </c>
       <c r="K5">
-        <v>0.008122777399974558</v>
+        <v>0.008361932440384261</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -637,34 +637,34 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>109.3357484381185</v>
+        <v>105.8903929694778</v>
       </c>
       <c r="C7">
-        <v>5.569988044827626</v>
+        <v>5.57001037685259</v>
       </c>
       <c r="D7">
-        <v>102.5239450725303</v>
+        <v>104.2453449799125</v>
       </c>
       <c r="E7">
-        <v>5.55941418820639</v>
+        <v>5.562231557288295</v>
       </c>
       <c r="F7">
-        <v>97.07732456162077</v>
+        <v>96.71255187981065</v>
       </c>
       <c r="G7">
-        <v>5.600602484146066</v>
+        <v>5.599512189499689</v>
       </c>
       <c r="H7">
-        <v>102.9790060240899</v>
+        <v>102.2827632764003</v>
       </c>
       <c r="I7">
-        <v>5.014814674953804</v>
+        <v>3.995579805569828</v>
       </c>
       <c r="J7">
-        <v>5.576668239060027</v>
+        <v>5.577251374546858</v>
       </c>
       <c r="K7">
-        <v>0.0174659225701656</v>
+        <v>0.01605792473571004</v>
       </c>
     </row>
     <row r="8" spans="1:11">
